--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260618.xlsx
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>24,658,155</t>
+          <t>125,081,205</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>125,081,205</t>
+          <t>24,658,155</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>57,121,834</t>
+          <t>35,009,788</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,009,788</t>
+          <t>57,121,834</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>37,501,266</t>
+          <t>25,671,885</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>25,671,885</t>
+          <t>37,501,266</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
